--- a/src/pandorafits/formats/nirda/level0_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level0_nirda.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chedges/Pandora/repos/pandora-fits/src/pandorafits/formats/nirda/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0EEFCDE-DC69-D741-AA45-54C8E43D159F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09A4E53-5E32-9840-97C3-D241E6C88387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34120" yWindow="-7640" windowWidth="30240" windowHeight="17220" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17260" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Structure" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="169">
   <si>
     <t>Extension</t>
   </si>
@@ -475,9 +475,6 @@
   </si>
   <si>
     <t>CCE Cold Tip2 Temperature at start of integrati</t>
-  </si>
-  <si>
-    <t>Conforms to FITS standard</t>
   </si>
   <si>
     <t>NAXIS1</t>
@@ -1586,7 +1583,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
@@ -1611,44 +1608,38 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>151</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
+        <v>151</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -1656,7 +1647,7 @@
         <v>152</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -1664,632 +1655,624 @@
         <v>153</v>
       </c>
       <c r="C6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
         <v>154</v>
-      </c>
-      <c r="C7" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>21</v>
+        <v>155</v>
       </c>
       <c r="B8" t="s">
-        <v>5</v>
+        <v>156</v>
       </c>
       <c r="C8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B9" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>157</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>158</v>
-      </c>
-      <c r="B10" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D18" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C20" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="D22" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D23" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D24" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C25" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D25" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D26" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C27" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D27" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C28" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D28" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D29" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D30" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C31" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D31" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C32" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D32" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C33" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D33" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C34" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D34" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C35" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="D35" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C36" t="s">
         <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C37" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="D37" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C38" t="s">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c r="D38" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C39" t="s">
         <v>47</v>
       </c>
       <c r="D39" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C40" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C41" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="D41" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C42" t="s">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="D42" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C43" t="s">
-        <v>18</v>
+        <v>114</v>
       </c>
       <c r="D43" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>113</v>
+        <v>158</v>
       </c>
       <c r="C44" t="s">
-        <v>114</v>
+        <v>159</v>
       </c>
       <c r="D44" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="C45" t="s">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="D45" t="s">
-        <v>161</v>
+        <v>118</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C46" t="s">
-        <v>117</v>
+        <v>47</v>
       </c>
       <c r="D46" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C47" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="D47" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C48" t="s">
         <v>18</v>
       </c>
       <c r="D48" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C49" t="s">
         <v>18</v>
       </c>
       <c r="D49" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C50" t="s">
-        <v>18</v>
+        <v>128</v>
       </c>
       <c r="D50" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C51" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D51" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C52" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="D52" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C53" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D53" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C54" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D54" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C55" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D55" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C56" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D56" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C57" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D57" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="C58" t="s">
-        <v>149</v>
+        <v>12</v>
       </c>
       <c r="D58" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>20</v>
-      </c>
-      <c r="C59" t="s">
-        <v>12</v>
-      </c>
-      <c r="D59" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A59" s="2" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="60" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A60" s="2" t="s">
+      <c r="B59" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="C59" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="D60" s="2" t="s">
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
         <v>165</v>
+      </c>
+      <c r="B60">
+        <v>0</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D61" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
         <v>168</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
-      </c>
-      <c r="C62">
-        <v>1</v>
-      </c>
-      <c r="D62" t="s">
-        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/src/pandorafits/formats/nirda/level0_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level0_nirda.xlsx
@@ -1554,12 +1554,12 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>cgrMedoMcdoMcdoM</t>
+          <t>bfoOedoLbdoLbdoL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:35</t>
+          <t>HDU checksum updated 2026-01-07T18:03:56</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:35</t>
+          <t>data unit checksum updated 2026-01-07T18:03:56</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fCa4hAS4fAY4fAY4</t>
+          <t>eBa6hAR3eAX3eAX3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:36</t>
+          <t>HDU checksum updated 2026-01-07T18:03:57</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:36</t>
+          <t>data unit checksum updated 2026-01-07T18:03:57</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/nirda/level0_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level0_nirda.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -766,7 +766,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>v3.01</t>
+          <t>v2.08</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -802,7 +802,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1278,7 +1278,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>INTEGRTS</t>
+          <t>GRPS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -1289,14 +1289,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SC_Integrations value for acquire</t>
+          <t>SC_Groups value for acquire</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EXPOSRES</t>
+          <t>INTEGRTS</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -1307,32 +1307,32 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>SC_Exposures value for acquire</t>
+          <t>SC_Integrations value for acquire</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ENDDELAY</t>
+          <t>EXPOSRES</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SC_EndDelay value for acquire</t>
+          <t>SC_Exposures value for acquire</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>RSTSINC</t>
+          <t>ENDDELAY</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1343,14 +1343,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Reset frames included in datacube?</t>
+          <t>SC_EndDelay value for acquire</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DRPSINC</t>
+          <t>RSTSINC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -1361,50 +1361,50 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Drop frames included in datacube?</t>
+          <t>Reset frames included in datacube?</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FRMSTOT</t>
+          <t>DRPSINC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Total #frames clocked in acquire</t>
+          <t>Drop frames included in datacube?</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FRMSEXP</t>
+          <t>FRMSTOT</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>#frames expected to be acquired from MACIE/SIDE</t>
+          <t>Total #frames clocked in acquire</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FRMSACQ</t>
+          <t>FRMSEXP</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -1415,169 +1415,187 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>#frames actually acquired from  MACIE/SIDECAR</t>
+          <t>#frames expected to be acquired from MACIE/SIDE</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GRPSAVGD</t>
+          <t>FRMSACQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Whether groups were averaged (1) or not (0)</t>
+          <t>#frames actually acquired from  MACIE/SIDECAR</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PAMPGAIN</t>
+          <t>GRPSAVGD</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Pre-amp gain based on gain register value.</t>
+          <t>Whether groups were averaged (1) or not (0)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FRMTIME</t>
+          <t>PAMPGAIN</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>10736</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Frame time in ms</t>
+          <t>Pre-amp gain based on gain register value.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TSIDECAR</t>
+          <t>FRMTIME</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>999.0</t>
+          <t>10736</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SIDECAR Temperature at start of integration</t>
+          <t>Frame time in ms</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TCOMPRJT</t>
+          <t>TSIDECAR</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>297.6682434082031</t>
+          <t>999.0</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CCE Compressor Reject Temperature at start of i</t>
+          <t>SIDECAR Temperature at start of integration</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TCLDTIP1</t>
+          <t>TCOMPRJT</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>78.88285064697266</t>
+          <t>297.6682434082031</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CCE Cold Tip1 Temperature at start of integrati</t>
+          <t>CCE Compressor Reject Temperature at start of i</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TCLDTIP2</t>
+          <t>TCLDTIP1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>68.87708282470703</t>
+          <t>78.88285064697266</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>CCE Cold Tip2 Temperature at start of integrati</t>
+          <t>CCE Cold Tip1 Temperature at start of integrati</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
+          <t>TCLDTIP2</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>bfoOedoLbdoLbdoL</t>
+          <t>68.87708282470703</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:56</t>
+          <t>CCE Cold Tip2 Temperature at start of integrati</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DATASUM</t>
+          <t>CHECKSUM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
+          <t>JSgZKRZWJRfWJRZW</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-08T14:08:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-07T18:03:56</t>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-08T14:08:01</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1846,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>eBa6hAR3eAX3eAX3</t>
+          <t>eEZ6gCX6eCX6eCX6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:57</t>
+          <t>HDU checksum updated 2026-01-08T14:08:02</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1869,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:57</t>
+          <t>data unit checksum updated 2026-01-08T14:08:02</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/nirda/level0_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level0_nirda.xlsx
@@ -1572,12 +1572,12 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>JSgZKRZWJRfWJRZW</t>
+          <t>LUeYORbXLRbXLRbX</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:08:01</t>
+          <t>HDU checksum updated 2026-01-16T10:20:00</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:08:01</t>
+          <t>data unit checksum updated 2026-01-16T10:20:00</t>
         </is>
       </c>
     </row>
@@ -1846,12 +1846,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>eEZ6gCX6eCX6eCX6</t>
+          <t>hDa8hDU6hDa6hDU6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:08:02</t>
+          <t>HDU checksum updated 2026-01-16T10:20:01</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:08:02</t>
+          <t>data unit checksum updated 2026-01-16T10:20:01</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/nirda/level0_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level0_nirda.xlsx
@@ -1572,12 +1572,12 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LUeYORbXLRbXLRbX</t>
+          <t>LQdXNPbULPbULPbU</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:20:00</t>
+          <t>HDU checksum updated 2026-01-16T15:40:13</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:20:00</t>
+          <t>data unit checksum updated 2026-01-16T15:40:13</t>
         </is>
       </c>
     </row>
@@ -1846,12 +1846,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>hDa8hDU6hDa6hDU6</t>
+          <t>gBa6jAV3gAZ3gAZ3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:20:01</t>
+          <t>HDU checksum updated 2026-01-16T15:40:15</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:20:01</t>
+          <t>data unit checksum updated 2026-01-16T15:40:15</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/nirda/level0_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level0_nirda.xlsx
@@ -766,7 +766,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>v2.08</t>
+          <t>v3.03</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -802,7 +802,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -818,7 +818,11 @@
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HAT-P-26b</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>Target ID/keyword</t>
@@ -834,7 +838,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/sssp/data/2025/04/05/2025-04-05__13-15-18_InfImg_d2048x2048x0050_b1_e01_i01_g01_d00_r50.sp</t>
+          <t>/sssp/data/2026/04/01/2026-04-01__00-03-18_InfImg_HAT-P-26b_d0200x0600x0472_b1_e01_i59_g02_d16_r04.sp</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -906,7 +910,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1610</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -924,7 +928,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>750</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -960,7 +964,7 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>200</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -978,7 +982,7 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>600</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -996,7 +1000,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>118</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1032,7 +1036,7 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1050,7 +1054,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>797174156</t>
+          <t>828317035</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1068,7 +1072,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>738000000</t>
+          <t>818000000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1230,7 +1234,7 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1266,7 +1270,7 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1284,7 +1288,7 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1302,7 +1306,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1392,7 +1396,7 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1410,7 +1414,7 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>472</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1428,7 +1432,7 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>472</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1446,7 +1450,7 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1464,7 +1468,7 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.65685</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1482,7 +1486,7 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10736</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1500,7 +1504,7 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>999.0</t>
+          <t>-2.6456665992736816</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1518,7 +1522,7 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>297.6682434082031</t>
+          <t>264.48187255859375</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1536,7 +1540,7 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>78.88285064697266</t>
+          <t>138.0994873046875</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1554,7 +1558,7 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>68.87708282470703</t>
+          <t>127.01375579833984</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1572,12 +1576,12 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LQdXNPbULPbULPbU</t>
+          <t>GY7FIW79GW7CGW79</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:40:13</t>
+          <t>HDU checksum updated 2026-04-08T14:21:24</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1599,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:40:13</t>
+          <t>data unit checksum updated 2026-04-08T14:21:24</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1714,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>200</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -1724,7 +1728,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>600</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -1738,7 +1742,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>118</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1846,12 +1850,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>gBa6jAV3gAZ3gAZ3</t>
+          <t>WEfAa9d3YCdAa9d3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T15:40:15</t>
+          <t>HDU checksum updated 2026-04-08T14:21:24</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1868,12 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1494830781</t>
+          <t>2131261651</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T15:40:15</t>
+          <t>data unit checksum updated 2026-04-08T14:21:24</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/nirda/level0_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level0_nirda.xlsx
@@ -820,7 +820,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HAT-P-26b</t>
+          <t>WASP-178b</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -838,7 +838,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/sssp/data/2026/04/01/2026-04-01__00-03-18_InfImg_HAT-P-26b_d0200x0600x0472_b1_e01_i59_g02_d16_r04.sp</t>
+          <t>/sssp/data/2026/05/08/2026-05-08__01-26-18_InfImg_WASP-178b_d0080x0400x1488_b1_e01_i62_g06_d16_r04.sp</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -910,7 +910,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1610</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -928,7 +928,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>907</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -964,7 +964,7 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -982,7 +982,7 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1000,7 +1000,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>372</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1054,7 +1054,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>828317035</t>
+          <t>831518815</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1072,7 +1072,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>818000000</t>
+          <t>835000000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1180,7 +1180,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1216,7 +1216,7 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1288,7 +1288,7 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1306,7 +1306,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1396,7 +1396,7 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>6621</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1414,7 +1414,7 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1432,7 +1432,7 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>1488</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1486,7 +1486,7 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>369</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1504,7 +1504,7 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>-2.6456665992736816</t>
+          <t>-3.4849305152893066</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1522,7 +1522,7 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>264.48187255859375</t>
+          <t>261.29901123046875</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1540,7 +1540,7 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>138.0994873046875</t>
+          <t>136.4371337890625</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1558,7 +1558,7 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>127.01375579833984</t>
+          <t>126.43830871582031</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1576,12 +1576,12 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GY7FIW79GW7CGW79</t>
+          <t>YG9mZG6lYG6lYG6l</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-04-08T14:21:24</t>
+          <t>HDU checksum updated 2026-06-10T14:51:09</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-04-08T14:21:24</t>
+          <t>data unit checksum updated 2026-06-10T14:51:09</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -1728,7 +1728,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -1742,7 +1742,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>372</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1850,12 +1850,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>WEfAa9d3YCdAa9d3</t>
+          <t>ZIbAfIb4ZIbAdIb3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-04-08T14:21:24</t>
+          <t>HDU checksum updated 2026-06-10T14:51:09</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2131261651</t>
+          <t>741039595</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-04-08T14:21:24</t>
+          <t>data unit checksum updated 2026-06-10T14:51:09</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/nirda/level0_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level0_nirda.xlsx
@@ -766,7 +766,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>v3.03</t>
+          <t>v3.06</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -820,7 +820,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>WASP-178b</t>
+          <t>WASP-18b</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -838,7 +838,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/sssp/data/2026/05/08/2026-05-08__01-26-18_InfImg_WASP-178b_d0080x0400x1488_b1_e01_i62_g06_d16_r04.sp</t>
+          <t>/sssp/data/2026/06/30/2026-06-30__15-36-18_InfImg_WASP-18b_d0080x0250x2184_b1_e01_i91_g06_d16_r04.sp</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -928,7 +928,7 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>907</t>
+          <t>962</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -982,7 +982,7 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>250</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1000,7 +1000,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>546</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1054,7 +1054,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>831518815</t>
+          <t>836149015</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1072,7 +1072,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>835000000</t>
+          <t>860000000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1180,7 +1180,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>261</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1306,7 +1306,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1396,7 +1396,7 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>9906</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1414,7 +1414,7 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1432,7 +1432,7 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1488</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1486,7 +1486,7 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>231</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1504,7 +1504,7 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>-3.4849305152893066</t>
+          <t>-8.405950546264648</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1522,7 +1522,7 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>261.29901123046875</t>
+          <t>277.5338134765625</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1540,7 +1540,7 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>136.4371337890625</t>
+          <t>131.91334533691406</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1558,7 +1558,7 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>126.43830871582031</t>
+          <t>120.00798797607422</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1576,12 +1576,12 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>YG9mZG6lYG6lYG6l</t>
+          <t>boqPclnOblnOblnO</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-06-10T14:51:09</t>
+          <t>HDU checksum updated 2026-07-15T15:20:52</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-06-10T14:51:09</t>
+          <t>data unit checksum updated 2026-07-15T15:20:52</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>250</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -1742,7 +1742,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>546</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1850,12 +1850,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ZIbAfIb4ZIbAdIb3</t>
+          <t>7fhlAZfl0dfl7Zfl</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-06-10T14:51:09</t>
+          <t>HDU checksum updated 2026-07-15T15:20:52</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>741039595</t>
+          <t>3372590735</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-06-10T14:51:09</t>
+          <t>data unit checksum updated 2026-07-15T15:20:52</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/nirda/level0_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level0_nirda.xlsx
@@ -838,7 +838,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/sssp/data/2026/06/30/2026-06-30__15-36-18_InfImg_WASP-18b_d0080x0250x2184_b1_e01_i91_g06_d16_r04.sp</t>
+          <t>/sssp/data/2026/06/30/2026-06-30__07-32-18_InfImg_WASP-18b_d0080x0250x2184_b1_e01_i91_g06_d16_r04.sp</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1054,7 +1054,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>836149015</t>
+          <t>836119976</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1072,7 +1072,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>860000000</t>
+          <t>284000000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1504,7 +1504,7 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>-8.405950546264648</t>
+          <t>-8.596685409545898</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1522,7 +1522,7 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>277.5338134765625</t>
+          <t>278.990966796875</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1540,7 +1540,7 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>131.91334533691406</t>
+          <t>131.82008361816406</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1558,7 +1558,7 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>120.00798797607422</t>
+          <t>120.00270080566406</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1576,12 +1576,12 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>boqPclnOblnOblnO</t>
+          <t>Yg9Ncd7NZd7Nad7N</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-15T15:20:52</t>
+          <t>HDU checksum updated 2026-07-23T15:43:43</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-15T15:20:52</t>
+          <t>data unit checksum updated 2026-07-23T15:43:43</t>
         </is>
       </c>
     </row>
@@ -1850,12 +1850,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7fhlAZfl0dfl7Zfl</t>
+          <t>cAAPc5APcAAPc3AP</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-15T15:20:52</t>
+          <t>HDU checksum updated 2026-07-23T15:43:43</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3372590735</t>
+          <t>1520241884</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-15T15:20:52</t>
+          <t>data unit checksum updated 2026-07-23T15:43:43</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/nirda/level0_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level0_nirda.xlsx
@@ -820,7 +820,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>WASP-18b</t>
+          <t>HD_200654</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -838,7 +838,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/sssp/data/2026/06/30/2026-06-30__07-32-18_InfImg_WASP-18b_d0080x0250x2184_b1_e01_i91_g06_d16_r04.sp</t>
+          <t>/sssp/data/2026/08/15/2026-08-15__03-03-20_InfImg_HD_200654_d0080x0250x1583_b1_e01_i427_g02_d16_r04.sp</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1000,7 +1000,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>394</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1054,7 +1054,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>836119976</t>
+          <t>840078241</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1072,7 +1072,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>284000000</t>
+          <t>877000000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1180,7 +1180,7 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>259</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1288,7 +1288,7 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1306,7 +1306,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>427</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1396,7 +1396,7 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>9906</t>
+          <t>11360</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1414,7 +1414,7 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2184</t>
+          <t>3416</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1432,7 +1432,7 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2184</t>
+          <t>1583</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1504,7 +1504,7 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>-8.596685409545898</t>
+          <t>0.5968567132949829</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1522,7 +1522,7 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>278.990966796875</t>
+          <t>276.0766906738281</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1540,7 +1540,7 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>131.82008361816406</t>
+          <t>131.3281707763672</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1558,7 +1558,7 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>120.00270080566406</t>
+          <t>120.02909851074219</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1576,12 +1576,12 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Yg9Ncd7NZd7Nad7N</t>
+          <t>oi2Uqg1Sog1Sog1S</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-23T15:43:43</t>
+          <t>HDU checksum updated 2026-08-25T21:26:25</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-23T15:43:43</t>
+          <t>data unit checksum updated 2026-08-25T21:26:25</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>394</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1850,12 +1850,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>cAAPc5APcAAPc3AP</t>
+          <t>LZYaOYWULYWaLYWU</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-07-23T15:43:43</t>
+          <t>HDU checksum updated 2026-08-25T21:26:25</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1520241884</t>
+          <t>4231325753</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-07-23T15:43:43</t>
+          <t>data unit checksum updated 2026-08-25T21:26:25</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/nirda/level0_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level0_nirda.xlsx
@@ -1576,12 +1576,12 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>oi2Uqg1Sog1Sog1S</t>
+          <t>0h2U1f2R0f2R0f2R</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:25</t>
+          <t>HDU checksum updated 2026-09-08T14:41:25</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:25</t>
+          <t>data unit checksum updated 2026-09-08T14:41:25</t>
         </is>
       </c>
     </row>
@@ -1850,12 +1850,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LZYaOYWULYWaLYWU</t>
+          <t>MYYZOXXZMXXZMXXZ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:25</t>
+          <t>HDU checksum updated 2026-09-08T14:41:25</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:25</t>
+          <t>data unit checksum updated 2026-09-08T14:41:25</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/nirda/level0_nirda.xlsx
+++ b/src/pandorafits/formats/nirda/level0_nirda.xlsx
@@ -820,7 +820,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HD_200654</t>
+          <t>KELT-9b</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -838,7 +838,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>/sssp/data/2026/08/15/2026-08-15__03-03-20_InfImg_HD_200654_d0080x0250x1583_b1_e01_i427_g02_d16_r04.sp</t>
+          <t>/sssp/data/2026/08/15/2026-08-15__06-44-18_InfImg_KELT-9b_d0080x0250x3096_b1_e01_i387_g02_d16_r04.sp</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1000,7 +1000,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>774</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1054,7 +1054,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>840078241</t>
+          <t>840091495</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1072,7 +1072,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>877000000</t>
+          <t>832000000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1306,7 +1306,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>427</t>
+          <t>387</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1396,7 +1396,7 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>11360</t>
+          <t>10320</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1414,7 +1414,7 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1432,7 +1432,7 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1504,7 +1504,7 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>0.5968567132949829</t>
+          <t>3.3816466331481934</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1522,7 +1522,7 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>276.0766906738281</t>
+          <t>278.990966796875</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1540,7 +1540,7 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>131.3281707763672</t>
+          <t>131.50372314453125</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1558,7 +1558,7 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>120.02909851074219</t>
+          <t>120.03438568115234</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1576,12 +1576,12 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>0h2U1f2R0f2R0f2R</t>
+          <t>08m736k506k506k5</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:25</t>
+          <t>HDU checksum updated 2026-09-09T15:45:53</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:25</t>
+          <t>data unit checksum updated 2026-09-09T15:45:53</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>394</t>
+          <t>774</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1850,12 +1850,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MYYZOXXZMXXZMXXZ</t>
+          <t>oDGar9FVoCFZo9FZ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:25</t>
+          <t>HDU checksum updated 2026-09-09T15:45:53</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4231325753</t>
+          <t>1450830242</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:25</t>
+          <t>data unit checksum updated 2026-09-09T15:45:53</t>
         </is>
       </c>
     </row>
